--- a/个人专属数据空间_功能清单.xlsx
+++ b/个人专属数据空间_功能清单.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1530,25 +1530,30 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>后台管理</t>
+          <t>工作台</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>用户管理</t>
+          <t>智能工作台</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>查看App端注册用户信息及实名状态</t>
+          <t>指标概览</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>展示平台核心指标（注册数、认领数据量、自有数据上传量、服务应用数量、授权数等）。</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
           <t>Admin端</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>管理员权限</t>
         </is>
@@ -1557,25 +1562,30 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>后台管理</t>
+          <t>工作台</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>数据目录管理</t>
+          <t>智能工作台</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>配置可供认领和接入的数据源目录</t>
+          <t>待办事项</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>聚合展示待处理工单、告警信息。</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
           <t>Admin端</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>管理员权限</t>
         </is>
@@ -1584,25 +1594,30 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>后台管理</t>
+          <t>工作台</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>纠错审核</t>
+          <t>智能工作台</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>审核用户提交的数据纠错申请，推进处理进度</t>
+          <t>AI每日运营简报</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>基于大模型能力，每天自动生成一段自然语言的系统运营简报，辅助管理者快速掌握全局。</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>Admin端</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>管理员权限</t>
         </is>
@@ -1611,25 +1626,30 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>后台管理</t>
+          <t>数据检索管理</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>授权模板管理</t>
+          <t>数据检索</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>配置不同场景下的数据授权范围和模板</t>
+          <t>数据检索</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>对人口数据进行检索，支持关键词检索、组合检索、高级检索</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
           <t>Admin端</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>管理员权限</t>
         </is>
@@ -1638,25 +1658,293 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>数据检索管理</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>数据检索</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>AI语义检索</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>【AI结合】突破传统SQL查询限制，管理员可通过自然语言提问，AI自动将自然语言转化为复杂查询逻辑，直接输出结果台账。</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Admin端</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>管理员权限</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>数据检索管理</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>数据检索</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>全息档案详情</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>360度展示市民基础信息、资产、健康等，支持敏感数据脱敏。</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Admin端</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>管理员权限</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>数据检索管理</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>数据检索</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>AI画像与智能打标</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>【AI结合】接入AI知识图谱，后台自动对“一人一档”数据进行运算，为市民自动打上隐性标签，为精准施政提供依据。</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Admin端</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>管理员权限</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>数据检索管理</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>数图分析/社区地图</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>3D人口态势大屏</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>以GIS/3D地图宏观展示人口分布热力图，包含不同年龄段人口占比、性别分布情况、民族分布情况、人口增长状况等。</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Admin端</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>管理员权限</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>数据检索管理</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>数图分析/社区地图</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>AI态势预测与推演</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>【AI结合】结合历史人口迁徙、出生率、社保缴纳等数据，利用机器学习算法预测未来3-5年的趋势。</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Admin端</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>管理员权限</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
           <t>后台管理</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>用户管理</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>查看App端注册用户信息及实名状态</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Admin端</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>管理员权限</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>后台管理</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>数据目录管理</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>配置可供认领和接入的数据源目录</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Admin端</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>管理员权限</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>后台管理</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>纠错审核</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>审核用户提交的数据纠错申请，推进处理进度</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Admin端</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>管理员权限</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>后台管理</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>授权模板管理</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>配置不同场景下的数据授权范围和模板</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Admin端</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>管理员权限</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>后台管理</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>系统设置</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>平台基础配置、角色权限分配等</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Admin端</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>管理员权限</t>
         </is>
